--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2023_biobio.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2023_biobio.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 16:44</t>
+    <t xml:space="preserve">2026-09-09 19:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2023_biobio.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2023_biobio.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:09</t>
+    <t xml:space="preserve">2026-09-17 04:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2023_biobio.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2023_biobio.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 04:24</t>
+    <t xml:space="preserve">2026-09-25 11:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2023_biobio.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2023_biobio.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 11:19</t>
+    <t xml:space="preserve">2026-09-27 02:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2023_biobio.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2023_biobio.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">Reg_Mujeres</t>
   </si>
   <si>
-    <t xml:space="preserve">Biobio</t>
+    <t xml:space="preserve">Biobío</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 02:08</t>
+    <t xml:space="preserve">2026-10-05 05:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Biobio</t>
+    <t xml:space="preserve">Region de Biobío</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">Arauco</t>
   </si>
   <si>
-    <t xml:space="preserve">Bíobío</t>
+    <t xml:space="preserve">Bío-Bío</t>
   </si>
 </sst>
 </file>
